--- a/APIS/Results/ComResult.xlsx
+++ b/APIS/Results/ComResult.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Programming\Asp\CSharp\MinimalApi\APIS\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7C0BCB-8FB6-4532-A077-DDD38BCA7D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A06AED3-CC3F-4C3F-B000-E350802DC4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,12 +38,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>ANNUAL REPORT</t>
   </si>
@@ -156,10 +159,13 @@
     <t>SHAHEEN BANO MOHAMMAD ALI</t>
   </si>
   <si>
-    <t>13TH JUNE 2025</t>
-  </si>
-  <si>
-    <t>MISS ANSARI BABY TABASSUM</t>
+    <t>2025 - 2026</t>
+  </si>
+  <si>
+    <t>15TH JUNE 2026</t>
+  </si>
+  <si>
+    <t>Ms. ANSARI BABY TABASSUM</t>
   </si>
 </sst>
 </file>
@@ -774,7 +780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -908,6 +914,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1004,14 +1019,11 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1303,42 +1315,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="66"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="69"/>
     </row>
     <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="73"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="76"/>
     </row>
     <row r="3" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
@@ -1358,23 +1370,23 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="70"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
     </row>
     <row r="5" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3"/>
@@ -1383,9 +1395,11 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="G5" s="90" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -1395,18 +1409,18 @@
       <c r="P5" s="4"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="81"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="84"/>
       <c r="K6" s="24" t="s">
         <v>17</v>
       </c>
@@ -1421,22 +1435,22 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="76"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="78"/>
+      <c r="A7" s="79"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="81"/>
       <c r="K7" s="22" t="s">
         <v>30</v>
       </c>
       <c r="L7" s="27"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="89"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
@@ -1459,10 +1473,10 @@
       <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:16" s="8" customFormat="1" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="85"/>
+      <c r="B10" s="88"/>
       <c r="C10" s="28" t="s">
         <v>7</v>
       </c>
@@ -1493,17 +1507,17 @@
       <c r="L10" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="55" t="s">
+      <c r="M10" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="56"/>
+      <c r="N10" s="59"/>
       <c r="O10" s="9"/>
     </row>
     <row r="11" spans="1:16" s="10" customFormat="1" ht="37.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="83"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="32">
         <v>100</v>
       </c>
@@ -1531,16 +1545,16 @@
       <c r="K11" s="33">
         <v>600</v>
       </c>
-      <c r="L11" s="57"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="58"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="61"/>
       <c r="O11" s="11"/>
     </row>
     <row r="12" spans="1:16" s="12" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="83"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="32">
         <v>35</v>
       </c>
@@ -1564,16 +1578,16 @@
       <c r="K12" s="33">
         <v>210</v>
       </c>
-      <c r="L12" s="59"/>
-      <c r="M12" s="59"/>
-      <c r="N12" s="60"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="63"/>
       <c r="O12" s="13"/>
     </row>
     <row r="13" spans="1:16" s="14" customFormat="1" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="75"/>
+      <c r="B13" s="78"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -1583,9 +1597,9 @@
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
       <c r="K13" s="16"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
-      <c r="N13" s="62"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="65"/>
       <c r="O13" s="17"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1644,7 +1658,7 @@
       </c>
       <c r="L17" s="19"/>
       <c r="M17" s="51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N17" s="19"/>
       <c r="O17" s="20"/>
@@ -1689,10 +1703,10 @@
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
-      <c r="J21" s="86" t="s">
+      <c r="J21" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="86"/>
+      <c r="K21" s="89"/>
       <c r="L21" s="35"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1707,10 +1721,10 @@
       <c r="G22" s="37"/>
       <c r="H22" s="37"/>
       <c r="I22" s="38"/>
-      <c r="J22" s="87" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="87"/>
+      <c r="J22" s="91" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22" s="55"/>
       <c r="L22" s="37"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1728,14 +1742,14 @@
       <c r="L23" s="37"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="69"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="72"/>
       <c r="G24" s="39" t="s">
         <v>14</v>
       </c>
@@ -1754,9 +1768,9 @@
       <c r="L24" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="66"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="42" t="s">
@@ -1852,7 +1866,7 @@
       <c r="I32" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="M11:N13"/>
     <mergeCell ref="L11:L13"/>
@@ -1868,6 +1882,7 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape"/>

--- a/APIS/Results/ComResult.xlsx
+++ b/APIS/Results/ComResult.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Programming\Asp\CSharp\MinimalApi\APIS\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A06AED3-CC3F-4C3F-B000-E350802DC4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C304E9-A779-470F-A5A4-5CA8DC6230A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,6 +30,7 @@
     <definedName name="XRollNo">Sheet1!$M$7</definedName>
     <definedName name="XSP_MATHS">Sheet1!$H$13</definedName>
     <definedName name="XStudentName">Sheet1!$A$7</definedName>
+    <definedName name="XTEACHERREMARK">Sheet1!$C$17</definedName>
     <definedName name="XTOTAL">Sheet1!$K$13</definedName>
     <definedName name="XUR_HN_IT">Sheet1!$D$13</definedName>
   </definedNames>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>ANNUAL REPORT</t>
   </si>
@@ -166,6 +167,9 @@
   </si>
   <si>
     <t>Ms. ANSARI BABY TABASSUM</t>
+  </si>
+  <si>
+    <t>/189</t>
   </si>
 </sst>
 </file>
@@ -923,6 +927,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1021,9 +1028,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1304,6 +1308,7 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" customWidth="1"/>
@@ -1315,42 +1320,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="69"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="70"/>
     </row>
     <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="77"/>
     </row>
     <row r="3" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
@@ -1370,23 +1375,23 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
     </row>
     <row r="5" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3"/>
@@ -1395,11 +1400,11 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="90" t="s">
+      <c r="G5" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -1409,18 +1414,18 @@
       <c r="P5" s="4"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="84"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="85"/>
       <c r="K6" s="24" t="s">
         <v>17</v>
       </c>
@@ -1435,16 +1440,16 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="79"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="81"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="82"/>
       <c r="K7" s="22" t="s">
         <v>30</v>
       </c>
@@ -1473,10 +1478,10 @@
       <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:16" s="8" customFormat="1" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="88"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="28" t="s">
         <v>7</v>
       </c>
@@ -1507,17 +1512,17 @@
       <c r="L10" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="58" t="s">
+      <c r="M10" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="59"/>
+      <c r="N10" s="60"/>
       <c r="O10" s="9"/>
     </row>
     <row r="11" spans="1:16" s="10" customFormat="1" ht="37.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="86"/>
+      <c r="B11" s="87"/>
       <c r="C11" s="32">
         <v>100</v>
       </c>
@@ -1545,16 +1550,16 @@
       <c r="K11" s="33">
         <v>600</v>
       </c>
-      <c r="L11" s="60"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="61"/>
+      <c r="N11" s="62"/>
       <c r="O11" s="11"/>
     </row>
     <row r="12" spans="1:16" s="12" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="86"/>
+      <c r="B12" s="87"/>
       <c r="C12" s="32">
         <v>35</v>
       </c>
@@ -1578,16 +1583,16 @@
       <c r="K12" s="33">
         <v>210</v>
       </c>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="64"/>
       <c r="O12" s="13"/>
     </row>
     <row r="13" spans="1:16" s="14" customFormat="1" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="78"/>
+      <c r="B13" s="79"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -1597,9 +1602,9 @@
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
       <c r="K13" s="16"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="66"/>
       <c r="O13" s="17"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1652,7 +1657,9 @@
         <v>20</v>
       </c>
       <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
+      <c r="I17" s="19" t="s">
+        <v>40</v>
+      </c>
       <c r="K17" s="19" t="s">
         <v>21</v>
       </c>
@@ -1703,10 +1710,10 @@
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
-      <c r="J21" s="89" t="s">
+      <c r="J21" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="89"/>
+      <c r="K21" s="90"/>
       <c r="L21" s="35"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1721,7 +1728,7 @@
       <c r="G22" s="37"/>
       <c r="H22" s="37"/>
       <c r="I22" s="38"/>
-      <c r="J22" s="91" t="s">
+      <c r="J22" s="58" t="s">
         <v>39</v>
       </c>
       <c r="K22" s="55"/>
@@ -1742,14 +1749,14 @@
       <c r="L23" s="37"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="72"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="73"/>
       <c r="G24" s="39" t="s">
         <v>14</v>
       </c>
@@ -1768,9 +1775,9 @@
       <c r="L24" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="67"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="42" t="s">
